--- a/submission/ЗАМЕРЫ_УСТОЙЧИВОСТИ.xlsx
+++ b/submission/ЗАМЕРЫ_УСТОЙЧИВОСТИ.xlsx
@@ -10012,7 +10012,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Исходный файл: workspace/pdf_other/vtb_2026_q1.pdf</t>
+          <t>Исходный файл: vtb_2026_q1.pdf</t>
         </is>
       </c>
     </row>
@@ -11183,7 +11183,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Исходный файл: workspace/pdf_other/tbank_2024_q4.pdf</t>
+          <t>Исходный файл: tbank_2024_q4.pdf</t>
         </is>
       </c>
     </row>
@@ -12354,7 +12354,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Исходный файл: workspace/pdf_other/tbank_2026_q1.pdf</t>
+          <t>Исходный файл: tbank_2026_q1.pdf</t>
         </is>
       </c>
     </row>
@@ -14696,7 +14696,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Исходный файл: workspace/pdf_other/tbank_2026_q2.pdf</t>
+          <t>Исходный файл: tbank_2026_q2.pdf</t>
         </is>
       </c>
     </row>
